--- a/data/round3_data.xlsx
+++ b/data/round3_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siyid\workspace\silicon_sampling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDA22C3-C57F-46B4-9619-210C855A1B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF4CD0E-6660-41C7-9C78-35648AFC991E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9219D0CD-9B5C-4CFA-868D-99E1F997292F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9219D0CD-9B5C-4CFA-868D-99E1F997292F}"/>
   </bookViews>
   <sheets>
     <sheet name="round3" sheetId="20" r:id="rId1"/>
@@ -9157,12 +9157,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -9177,8 +9183,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9787,7 +9794,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91A03660-CB7D-43AE-9014-BB9D772160F2}">
   <dimension ref="A1:AW414"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="22" width="11.44140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="11.44140625" collapsed="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -10205,31 +10216,31 @@
       <c r="AM3" t="s">
         <v>242</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="AN3" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="AO3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AP3" t="s">
+      <c r="AP3" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="AQ3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="AR3" t="s">
+      <c r="AR3" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AS3" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="AT3" t="s">
+      <c r="AT3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="AU3" t="s">
+      <c r="AU3" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="AV3" t="s">
+      <c r="AV3" s="1" t="s">
         <v>125</v>
       </c>
       <c r="AW3" t="s">
